--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0135.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0135.xlsx
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Haha! Ừ, ta biết. Trông chả sáng sủa gì đâu, nhưng thằng này lại hot đấy. Dân Soliskin từ khắp nơi kéo đến chơi.</t>
+          <t>Haha! Ừ, tao biết. Trông chả sáng sủa gì đâu, nhưng thằng này lại hot đấy. Dân Soliskin từ khắp nơi kéo đến chơi.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Nói rõ mục đích của cậu đi.</t>
+          <t>Nói rõ mục đích của mày đi.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Và ta sẽ giúp dịch, cứ để ta lo.</t>
+          <t>Và tao sẽ giúp dịch, cứ để tao lo.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Nói rõ mục đích của cậu đi.</t>
+          <t>Nói rõ mục đích của mày đi.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>"Babu ở lại! Tacet Discord không bắt được ta đâu! Babu ở lại đợi mọi người về!"</t>
+          <t>"Babu ở lại! Tacet Discord không bắt được tao đâu! Babu ở lại đợi mọi người về!"</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Vậy là cậu với Chomp Chomp vận chuyển hàng cho Roya à?</t>
+          <t>Vậy là mày với Chomp Chomp vận chuyển hàng cho Roya à?</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Nếu chán gel năng lượng rồi, cứ đến tìm ta nhé.</t>
+          <t>Nếu chán gel năng lượng rồi, cứ đến tìm tao nhé.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Trước khi đến Dimmr Deep, ta cứ ngỡ chẳng ai thấy được mình đã cố gắng đến nhường nào.</t>
+          <t>Trước khi đến Dimmr Deep, tao cứ ngỡ chẳng ai thấy được mình đã cố gắng đến nhường nào.</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Giờ ta đã có đủ năng lượng rồi.</t>
+          <t>Giờ tao đã có đủ năng lượng rồi.</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Ta à? Ta muốn một thứ gì đó thực sự có ý nghĩa. Dù con đường có gian nan đến mấy.</t>
+          <t>Tao à? Tao muốn một thứ gì đó thực sự có ý nghĩa. Dù con đường có gian nan đến mấy.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Ta đã nộp đề xuất khảo sát Dimmr Deep cho Viện Nghiên cứu. Đồng thời đăng ký Chương trình Ươm tạo Spacetrek nữa.</t>
+          <t>Tao đã nộp đề xuất khảo sát Dimmr Deep cho Viện Nghiên cứu. Đồng thời đăng ký Chương trình Ươm tạo Spacetrek nữa.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Ta đã cấu hình trước mấy cái ở khu này cho hắn rồi... Ta đoán từ sớm là hắn không phải loại dễ bỏ cuộc đâu.</t>
+          <t>Tao đã cấu hình trước mấy cái ở khu này cho hắn rồi... Tao đoán từ sớm là hắn không phải loại dễ bỏ cuộc đâu.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đúng lúc FCR của ta lại hỏng... Thật là ác mộng... Uaaaagh...</t>
+          <t>Đúng lúc FCR của tao lại hỏng... Thật là ác mộng... Uaaaagh...</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Một lời nói dối vô hại à... Ta hiểu rồi. Giống như với Joss vậy.</t>
+          <t>Một lời nói dối vô hại à... Tao hiểu rồi. Giống như với Joss vậy.</t>
         </is>
       </c>
     </row>
